--- a/output/roomself_excel/14104.xlsx
+++ b/output/roomself_excel/14104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20532</v>
+        <v>184359</v>
       </c>
       <c r="D2" t="n">
-        <v>1172</v>
+        <v>3848</v>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>494</v>
       </c>
       <c r="F2" t="n">
-        <v>149</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>143472</v>
+        <v>243935</v>
       </c>
       <c r="D3" t="n">
-        <v>3128</v>
+        <v>5600</v>
       </c>
       <c r="E3" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="F3" t="n">
-        <v>521</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25480</v>
+        <v>127110</v>
       </c>
       <c r="D4" t="n">
-        <v>1288</v>
+        <v>2924</v>
       </c>
       <c r="E4" t="n">
-        <v>215</v>
+        <v>298</v>
       </c>
       <c r="F4" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>127110</v>
+        <v>84390</v>
       </c>
       <c r="D5" t="n">
-        <v>2924</v>
+        <v>2324</v>
       </c>
       <c r="E5" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
-        <v>298</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65970</v>
+        <v>29141</v>
       </c>
       <c r="D6" t="n">
-        <v>2864</v>
+        <v>1368</v>
       </c>
       <c r="E6" t="n">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39458</v>
+        <v>19980</v>
       </c>
       <c r="D7" t="n">
-        <v>1596</v>
+        <v>1172</v>
       </c>
       <c r="E7" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>113226</v>
+        <v>18980</v>
       </c>
       <c r="D8" t="n">
-        <v>2692</v>
+        <v>1104</v>
       </c>
       <c r="E8" t="n">
-        <v>561</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>414</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>507290</v>
+        <v>20532</v>
       </c>
       <c r="D9" t="n">
-        <v>9752</v>
+        <v>1172</v>
       </c>
       <c r="E9" t="n">
-        <v>979</v>
+        <v>210</v>
       </c>
       <c r="F9" t="n">
-        <v>636</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29141</v>
+        <v>77322</v>
       </c>
       <c r="D10" t="n">
-        <v>1368</v>
+        <v>2468</v>
       </c>
       <c r="E10" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32116</v>
+        <v>16352</v>
       </c>
       <c r="D11" t="n">
-        <v>1460</v>
+        <v>1032</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19980</v>
+        <v>25480</v>
       </c>
       <c r="D12" t="n">
-        <v>1172</v>
+        <v>1288</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>245180</v>
+        <v>32116</v>
       </c>
       <c r="D13" t="n">
-        <v>4032</v>
+        <v>1460</v>
       </c>
       <c r="E13" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32037</v>
+        <v>71350</v>
       </c>
       <c r="D14" t="n">
-        <v>1432</v>
+        <v>2388</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>462</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97067</v>
+        <v>143472</v>
       </c>
       <c r="D15" t="n">
-        <v>3104</v>
+        <v>3128</v>
       </c>
       <c r="E15" t="n">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="F15" t="n">
-        <v>209</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84390</v>
+        <v>65970</v>
       </c>
       <c r="D16" t="n">
-        <v>2324</v>
+        <v>2864</v>
       </c>
       <c r="E16" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16352</v>
+        <v>39458</v>
       </c>
       <c r="D17" t="n">
-        <v>1032</v>
+        <v>1596</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,108 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18980</v>
+        <v>113226</v>
       </c>
       <c r="D18" t="n">
-        <v>1104</v>
+        <v>2692</v>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>329</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1674</v>
+      </c>
+      <c r="D19" t="n">
+        <v>340</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>245180</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E20" t="n">
+        <v>628</v>
+      </c>
+      <c r="F20" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>32037</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1432</v>
+      </c>
+      <c r="E21" t="n">
+        <v>177</v>
+      </c>
+      <c r="F21" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25717</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1656</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14104.xlsx
+++ b/output/roomself_excel/14104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3848</v>
       </c>
-      <c r="E2" t="n">
-        <v>494</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>455</v>
+        <v>422</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>449</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>5600</v>
       </c>
-      <c r="E3" t="n">
-        <v>556</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>369</v>
+        <v>523</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>337</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2924</v>
       </c>
-      <c r="E4" t="n">
-        <v>298</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>298</v>
+        <v>285</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>446</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +609,26 @@
       <c r="D5" t="n">
         <v>2324</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>291</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>290</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>33</v>
       </c>
     </row>
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>1368</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>161</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>31</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +677,12 @@
       <c r="D7" t="n">
         <v>1172</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1104</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>130</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>33</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +729,27 @@
       <c r="D9" t="n">
         <v>1172</v>
       </c>
-      <c r="E9" t="n">
-        <v>210</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>177</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>116</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +767,12 @@
       <c r="D10" t="n">
         <v>2468</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,20 @@
       <c r="D11" t="n">
         <v>1032</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>112</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>33</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +819,27 @@
       <c r="D12" t="n">
         <v>1288</v>
       </c>
-      <c r="E12" t="n">
-        <v>215</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>155</v>
+        <v>182</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>122</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +857,20 @@
       <c r="D13" t="n">
         <v>1460</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="G13" t="n">
+        <v>31</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +887,27 @@
       <c r="D14" t="n">
         <v>2388</v>
       </c>
-      <c r="E14" t="n">
-        <v>462</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>195</v>
+        <v>165</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>431</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -761,11 +925,27 @@
       <c r="D15" t="n">
         <v>3128</v>
       </c>
-      <c r="E15" t="n">
-        <v>521</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>324</v>
+        <v>294</v>
+      </c>
+      <c r="G15" t="n">
+        <v>33</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>488</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -783,12 +963,12 @@
       <c r="D16" t="n">
         <v>2864</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +985,27 @@
       <c r="D17" t="n">
         <v>1596</v>
       </c>
-      <c r="E17" t="n">
-        <v>248</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>212</v>
+        <v>181</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>218</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1023,20 @@
       <c r="D18" t="n">
         <v>2692</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>329</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>30</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1053,12 @@
       <c r="D19" t="n">
         <v>340</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,11 +1075,27 @@
       <c r="D20" t="n">
         <v>4032</v>
       </c>
-      <c r="E20" t="n">
-        <v>628</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>440</v>
+        <v>410</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>598</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -893,12 +1113,20 @@
       <c r="D21" t="n">
         <v>1432</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>177</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>31</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1143,12 @@
       <c r="D22" t="n">
         <v>1656</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/14104.xlsx
+++ b/output/roomself_excel/14104.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,66 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +577,30 @@
       <c r="J2" t="n">
         <v>33</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>178</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +639,54 @@
       <c r="J3" t="n">
         <v>33</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>335</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>89</v>
+      </c>
+      <c r="R3" t="n">
+        <v>32</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>91</v>
+      </c>
+      <c r="V3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +725,30 @@
       <c r="J4" t="n">
         <v>31</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>174</v>
+      </c>
+      <c r="N4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,6 +787,30 @@
       <c r="J5" t="n">
         <v>33</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>161</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +841,30 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>93</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,6 +887,18 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -713,6 +929,30 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>61</v>
+      </c>
+      <c r="N8" t="n">
+        <v>33</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -751,6 +991,42 @@
       <c r="J9" t="n">
         <v>33</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>91</v>
+      </c>
+      <c r="N9" t="n">
+        <v>33</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>33</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -773,6 +1049,18 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -803,6 +1091,30 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>33</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -841,6 +1153,18 @@
       <c r="J12" t="n">
         <v>33</v>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -871,6 +1195,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -909,6 +1245,18 @@
       <c r="J14" t="n">
         <v>30</v>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -947,6 +1295,30 @@
       <c r="J15" t="n">
         <v>30</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>251</v>
+      </c>
+      <c r="N15" t="n">
+        <v>33</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -969,6 +1341,18 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1007,6 +1391,18 @@
       <c r="J17" t="n">
         <v>31</v>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1037,6 +1433,30 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>179</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1059,6 +1479,18 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1097,6 +1529,18 @@
       <c r="J20" t="n">
         <v>30</v>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1127,6 +1571,30 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>89</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1149,6 +1617,18 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
